--- a/Compititor's_Price/IKO_Prices/IKO_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_18-07-2025.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.71</t>
+          <t>£11.53</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£13.44</t>
+          <t>£13.25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£17.28</t>
+          <t>£16.99</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£22.26</t>
+          <t>£22.13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£24.29</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£30.45</t>
+          <t>£30.26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£30.45</t>
+          <t>£30.44</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£37.64</t>
+          <t>£36.74</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£46.73</t>
+          <t>£46.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">

--- a/Compititor's_Price/IKO_Prices/IKO_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_18-07-2025.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.71</t>
+          <t>£11.53</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£13.44</t>
+          <t>£13.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£17.28</t>
+          <t>£16.99</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£22.26</t>
+          <t>£22.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£24.29</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£30.45</t>
+          <t>£30.26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£30.45</t>
+          <t>£30.44</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£37.64</t>
+          <t>£36.74</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£37.64</t>
+          <t>£36.74</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£46.73</t>
+          <t>£46.19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£46.73</t>
+          <t>£46.19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">

--- a/Compititor's_Price/IKO_Prices/IKO_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_18-07-2025.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£11.71</t>
+          <t>£11.53</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£13.44</t>
+          <t>£13.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£17.28</t>
+          <t>£16.99</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£22.26</t>
+          <t>£22.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£24.29</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£30.45</t>
+          <t>£30.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£30.45</t>
+          <t>£30.44</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
